--- a/fixtures/daily-cash/테스트_전일일보.xlsx
+++ b/fixtures/daily-cash/테스트_전일일보.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="63">
   <si>
     <t xml:space="preserve">테스트 일일자금일보
 2026.10.12</t>
@@ -105,6 +105,9 @@
   </si>
   <si>
     <t>정기예금 현황(외화)</t>
+  </si>
+  <si>
+    <t>신탁현황</t>
   </si>
   <si>
     <t>주요 집행 내역</t>
@@ -1633,7 +1636,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="51" ht="42" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>28</v>
       </c>
@@ -2816,7 +2819,10 @@
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
-      <c r="D98" s="5"/>
+      <c r="D98" s="5">
+        <f>SUM(D51:D97)</f>
+        <v>0</v>
+      </c>
       <c r="E98" s="5"/>
       <c r="F98" s="4"/>
       <c r="G98" s="5"/>
@@ -3354,7 +3360,10 @@
       <c r="A120" s="4"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
-      <c r="D120" s="5"/>
+      <c r="D120" s="5">
+        <f>SUM(D102:D119)</f>
+        <v>0</v>
+      </c>
       <c r="E120" s="5"/>
       <c r="F120" s="4"/>
       <c r="G120" s="5"/>
@@ -3380,13 +3389,15 @@
       <c r="L121" s="4"/>
       <c r="M121" s="4"/>
     </row>
-    <row r="122" ht="22" customHeight="1" hidden="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A122" s="4"/>
-      <c r="B122" s="4"/>
-      <c r="C122" s="4"/>
+    <row r="122" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A122" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B122" s="5"/>
+      <c r="C122" s="5"/>
       <c r="D122" s="5"/>
       <c r="E122" s="5"/>
-      <c r="F122" s="4"/>
+      <c r="F122" s="5"/>
       <c r="G122" s="5"/>
       <c r="H122" s="5"/>
       <c r="I122" s="4"/>
@@ -3464,7 +3475,10 @@
       <c r="A126" s="4"/>
       <c r="B126" s="4"/>
       <c r="C126" s="4"/>
-      <c r="D126" s="5"/>
+      <c r="D126" s="5">
+        <f>SUM(D124:D125)</f>
+        <v>0</v>
+      </c>
       <c r="E126" s="5"/>
       <c r="F126" s="4"/>
       <c r="G126" s="5"/>
@@ -3492,7 +3506,7 @@
     </row>
     <row r="128" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -3524,15 +3538,15 @@
     </row>
     <row r="130" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B130" s="4"/>
       <c r="C130" s="4"/>
       <c r="D130" s="5"/>
       <c r="E130" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F130" s="4"/>
+        <v>34</v>
+      </c>
+      <c r="F130" s="5"/>
       <c r="G130" s="5"/>
       <c r="H130" s="5"/>
       <c r="I130" s="4"/>
@@ -3543,13 +3557,13 @@
     </row>
     <row r="131" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B131" s="4"/>
       <c r="C131" s="4"/>
       <c r="D131" s="5"/>
       <c r="E131" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F131" s="5"/>
       <c r="G131" s="5"/>
@@ -3940,13 +3954,13 @@
     </row>
     <row r="157" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B157" s="4"/>
       <c r="C157" s="4"/>
       <c r="D157" s="5"/>
       <c r="E157" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F157" s="5"/>
       <c r="G157" s="5"/>
@@ -5131,7 +5145,10 @@
       <c r="A236" s="4"/>
       <c r="B236" s="4"/>
       <c r="C236" s="4"/>
-      <c r="D236" s="5"/>
+      <c r="D236" s="5">
+        <f>SUM(D157:D235)</f>
+        <v>0</v>
+      </c>
       <c r="E236" s="5"/>
       <c r="F236" s="4"/>
       <c r="G236" s="5"/>
@@ -5144,15 +5161,15 @@
     </row>
     <row r="237" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B237" s="4"/>
       <c r="C237" s="4"/>
       <c r="D237" s="5"/>
       <c r="E237" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F237" s="4"/>
+        <v>38</v>
+      </c>
+      <c r="F237" s="5"/>
       <c r="G237" s="5"/>
       <c r="H237" s="5"/>
       <c r="I237" s="4"/>
@@ -5176,7 +5193,7 @@
       <c r="L238" s="4"/>
       <c r="M238" s="4"/>
       <c r="O238" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="239" ht="22" customHeight="1" hidden="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -5194,7 +5211,7 @@
       <c r="L239" s="4"/>
       <c r="M239" s="4"/>
       <c r="O239" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="240" ht="22" customHeight="1" hidden="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -5212,7 +5229,7 @@
       <c r="L240" s="4"/>
       <c r="M240" s="4"/>
       <c r="O240" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="241" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -5222,13 +5239,13 @@
       <c r="D241" s="5"/>
       <c r="E241" s="5"/>
       <c r="F241" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G241" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H241" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I241" s="4"/>
       <c r="J241" s="4"/>
@@ -5236,7 +5253,7 @@
       <c r="L241" s="4"/>
       <c r="M241" s="4"/>
       <c r="O241" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="242" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -5254,7 +5271,7 @@
       <c r="L242" s="4"/>
       <c r="M242" s="4"/>
       <c r="O242" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="243" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -5264,13 +5281,13 @@
       <c r="D243" s="5"/>
       <c r="E243" s="5"/>
       <c r="F243" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G243" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H243" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I243" s="4"/>
       <c r="J243" s="4"/>
@@ -5278,7 +5295,7 @@
       <c r="L243" s="4"/>
       <c r="M243" s="4"/>
       <c r="O243" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="244" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -5296,7 +5313,7 @@
       <c r="L244" s="4"/>
       <c r="M244" s="4"/>
       <c r="O244" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="245" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -5306,13 +5323,13 @@
       <c r="D245" s="5"/>
       <c r="E245" s="5"/>
       <c r="F245" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G245" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H245" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I245" s="4"/>
       <c r="J245" s="4"/>
@@ -5320,7 +5337,7 @@
       <c r="L245" s="4"/>
       <c r="M245" s="4"/>
       <c r="O245" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="246" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -5338,7 +5355,7 @@
       <c r="L246" s="4"/>
       <c r="M246" s="4"/>
       <c r="O246" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="247" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -5348,13 +5365,13 @@
       <c r="D247" s="2"/>
       <c r="E247" s="2"/>
       <c r="F247" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G247" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H247" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I247" s="3"/>
       <c r="J247" s="3"/>
@@ -5362,7 +5379,7 @@
       <c r="L247" s="3"/>
       <c r="M247" s="3"/>
       <c r="O247" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="248" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -5380,22 +5397,26 @@
       <c r="L248" s="4"/>
       <c r="M248" s="4"/>
       <c r="O248" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="249" spans="15:15" x14ac:dyDescent="0.25">
       <c r="O249" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="216">
+  <mergeCells count="222">
     <mergeCell ref="B2:H4"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="A49:G49"/>
+    <mergeCell ref="A51:B51"/>
     <mergeCell ref="A100:G100"/>
+    <mergeCell ref="A122:G122"/>
     <mergeCell ref="A128:G128"/>
+    <mergeCell ref="A130:C130"/>
+    <mergeCell ref="E130:G130"/>
     <mergeCell ref="B131:C131"/>
     <mergeCell ref="F131:G131"/>
     <mergeCell ref="B132:C132"/>
@@ -5606,6 +5627,8 @@
     <mergeCell ref="F234:G234"/>
     <mergeCell ref="B235:C235"/>
     <mergeCell ref="F235:G235"/>
+    <mergeCell ref="A237:C237"/>
+    <mergeCell ref="E237:G237"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
